--- a/DateBase/orders/Nhat 48_2026-7-3.xlsx
+++ b/DateBase/orders/Nhat 48_2026-7-3.xlsx
@@ -522,6 +522,9 @@
       <c r="A11" t="str">
         <v>3</v>
       </c>
+      <c r="C11" t="str">
+        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Nhat 48_2026-7-3.xlsx
+++ b/DateBase/orders/Nhat 48_2026-7-3.xlsx
@@ -525,6 +525,9 @@
       <c r="C11" t="str">
         <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -583,7 +586,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010807010132265130</v>
+        <v>010108070101322651337</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-7-3.xlsx
+++ b/DateBase/orders/Nhat 48_2026-7-3.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -529,9 +529,92 @@
         <v>37</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>611_康乃馨奶油白_cream white_undefined_20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>4</v>
+      </c>
+      <c r="C13" t="str">
+        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>217_琉璃翠_Dynamic_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>251_暖暖_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>611_康乃馨奶油白_cream white_undefined_20stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>5</v>
+      </c>
+      <c r="C18" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>18_波浪黄洋桔梗_Wavy Yellow Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -586,7 +669,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010108070101322651337</v>
+        <v>01010807010132265133713810131061020140</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-7-3.xlsx
+++ b/DateBase/orders/Nhat 48_2026-7-3.xlsx
@@ -611,6 +611,9 @@
       <c r="C21" t="str">
         <v>18_波浪黄洋桔梗_Wavy Yellow Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
+      <c r="F21" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -669,7 +672,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010807010132265133713810131061020140</v>
+        <v>010108070101322651337138101310610201410</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-7-3.xlsx
+++ b/DateBase/orders/Nhat 48_2026-7-3.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L26"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -615,9 +615,55 @@
         <v>10</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>6</v>
+      </c>
+      <c r="C22" t="str">
+        <v>18_波浪黄洋桔梗_Wavy Yellow Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>7</v>
+      </c>
+      <c r="C24" t="str">
+        <v>780_贝壳草_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>788_国产直葱白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L26"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -672,7 +718,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010108070101322651337138101310610201410</v>
+        <v>0101080701013226513371381013106102014101025151212</v>
       </c>
     </row>
   </sheetData>
